--- a/2022 data/excel_outputs/277_boothwise_data.xlsx
+++ b/2022 data/excel_outputs/277_boothwise_data.xlsx
@@ -14,11 +14,77 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="484">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="510" uniqueCount="506">
   <si>
     <t>AC 277 Booth-wise Data</t>
   </si>
   <si>
+    <t>Unnamed: 1</t>
+  </si>
+  <si>
+    <t>Unnamed: 2</t>
+  </si>
+  <si>
+    <t>Unnamed: 3</t>
+  </si>
+  <si>
+    <t>Unnamed: 4</t>
+  </si>
+  <si>
+    <t>Unnamed: 5</t>
+  </si>
+  <si>
+    <t>Unnamed: 6</t>
+  </si>
+  <si>
+    <t>Unnamed: 7</t>
+  </si>
+  <si>
+    <t>Unnamed: 8</t>
+  </si>
+  <si>
+    <t>Unnamed: 9</t>
+  </si>
+  <si>
+    <t>Unnamed: 10</t>
+  </si>
+  <si>
+    <t>Unnamed: 11</t>
+  </si>
+  <si>
+    <t>Unnamed: 12</t>
+  </si>
+  <si>
+    <t>Unnamed: 13</t>
+  </si>
+  <si>
+    <t>Unnamed: 14</t>
+  </si>
+  <si>
+    <t>Unnamed: 15</t>
+  </si>
+  <si>
+    <t>Unnamed: 16</t>
+  </si>
+  <si>
+    <t>Unnamed: 17</t>
+  </si>
+  <si>
+    <t>Unnamed: 18</t>
+  </si>
+  <si>
+    <t>Unnamed: 19</t>
+  </si>
+  <si>
+    <t>Unnamed: 20</t>
+  </si>
+  <si>
+    <t>Unnamed: 21</t>
+  </si>
+  <si>
+    <t>Unnamed: 22</t>
+  </si>
+  <si>
     <t>BOOTH ID</t>
   </si>
   <si>
@@ -901,13 +967,13 @@
     <t>SHANTI ASHARAM INTER COLLGER SAYA KAKSH NO. 1</t>
   </si>
   <si>
-    <t>SHANTI ASHARAM INTER COLLEGE. SAYA KAKSH NO. ■</t>
+    <t>PRA0PA0 PAMOLI</t>
   </si>
   <si>
     <t>PRIMARY SCHOOL PICHHAWARA KAKSH NO. 1</t>
   </si>
   <si>
-    <t>PRIMARY SCHOOL PICHHAWARA KAKSH NO. ■</t>
+    <t>PRA0PA0DAHEMA</t>
   </si>
   <si>
     <t>PRIMARY SCHOOL MUSTAFABAD KAKSH NO. 1</t>
@@ -1472,8 +1538,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+  <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -1489,7 +1563,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -1497,12 +1571,30 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1801,79 +1893,145 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:23">
-      <c r="A1" t="s">
-        <v>0</v>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="2" spans="1:23">
       <c r="A2" t="s">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="B2" t="s">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="C2" t="s">
-        <v>463</v>
+        <v>485</v>
       </c>
       <c r="D2" t="s">
-        <v>464</v>
+        <v>486</v>
       </c>
       <c r="E2" t="s">
-        <v>465</v>
+        <v>487</v>
       </c>
       <c r="F2" t="s">
-        <v>466</v>
+        <v>488</v>
       </c>
       <c r="G2" t="s">
-        <v>467</v>
+        <v>489</v>
       </c>
       <c r="H2" t="s">
-        <v>468</v>
+        <v>490</v>
       </c>
       <c r="I2" t="s">
-        <v>469</v>
+        <v>491</v>
       </c>
       <c r="J2" t="s">
-        <v>470</v>
+        <v>492</v>
       </c>
       <c r="K2" t="s">
-        <v>471</v>
+        <v>493</v>
       </c>
       <c r="L2" t="s">
-        <v>472</v>
+        <v>494</v>
       </c>
       <c r="M2" t="s">
-        <v>473</v>
+        <v>495</v>
       </c>
       <c r="N2" t="s">
-        <v>474</v>
+        <v>496</v>
       </c>
       <c r="O2" t="s">
-        <v>475</v>
+        <v>497</v>
       </c>
       <c r="P2" t="s">
-        <v>476</v>
+        <v>498</v>
       </c>
       <c r="Q2" t="s">
-        <v>477</v>
+        <v>499</v>
       </c>
       <c r="R2" t="s">
-        <v>478</v>
+        <v>500</v>
       </c>
       <c r="S2" t="s">
-        <v>479</v>
+        <v>501</v>
       </c>
       <c r="T2" t="s">
-        <v>480</v>
+        <v>502</v>
       </c>
       <c r="U2" t="s">
-        <v>481</v>
+        <v>503</v>
       </c>
       <c r="V2" t="s">
-        <v>482</v>
+        <v>504</v>
       </c>
       <c r="W2" t="s">
-        <v>483</v>
+        <v>505</v>
       </c>
     </row>
     <row r="3" spans="1:23">
@@ -1881,7 +2039,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="C3">
         <v>1001</v>
@@ -1952,7 +2110,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="C4">
         <v>794</v>
@@ -2023,7 +2181,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="C5">
         <v>723</v>
@@ -2094,7 +2252,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="C6">
         <v>1187</v>
@@ -2165,7 +2323,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="C7">
         <v>927</v>
@@ -2236,7 +2394,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="C8">
         <v>834</v>
@@ -2307,7 +2465,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="C9">
         <v>755</v>
@@ -2378,7 +2536,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="C10">
         <v>1149</v>
@@ -2449,7 +2607,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="C11">
         <v>1071</v>
@@ -2520,7 +2678,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="C12">
         <v>1190</v>
@@ -2591,7 +2749,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="C13">
         <v>1182</v>
@@ -2662,7 +2820,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="C14">
         <v>904</v>
@@ -2733,7 +2891,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="C15">
         <v>964</v>
@@ -2804,7 +2962,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C16">
         <v>912</v>
@@ -2875,7 +3033,7 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="C17">
         <v>1116</v>
@@ -2946,7 +3104,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="C18">
         <v>605</v>
@@ -3017,7 +3175,7 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>19</v>
+        <v>41</v>
       </c>
       <c r="C19">
         <v>761</v>
@@ -3088,7 +3246,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="C20">
         <v>638</v>
@@ -3159,7 +3317,7 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>21</v>
+        <v>43</v>
       </c>
       <c r="C21">
         <v>893</v>
@@ -3230,7 +3388,7 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="C22">
         <v>861</v>
@@ -3301,7 +3459,7 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>23</v>
+        <v>45</v>
       </c>
       <c r="C23">
         <v>916</v>
@@ -3372,7 +3530,7 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="C24">
         <v>874</v>
@@ -3443,7 +3601,7 @@
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>25</v>
+        <v>47</v>
       </c>
       <c r="C25">
         <v>627</v>
@@ -3514,7 +3672,7 @@
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>26</v>
+        <v>48</v>
       </c>
       <c r="C26">
         <v>864</v>
@@ -3585,7 +3743,7 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>27</v>
+        <v>49</v>
       </c>
       <c r="C27">
         <v>1061</v>
@@ -3656,7 +3814,7 @@
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="C28">
         <v>516</v>
@@ -3727,7 +3885,7 @@
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>29</v>
+        <v>51</v>
       </c>
       <c r="C29">
         <v>1075</v>
@@ -3798,7 +3956,7 @@
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>30</v>
+        <v>52</v>
       </c>
       <c r="C30">
         <v>692</v>
@@ -3869,7 +4027,7 @@
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>31</v>
+        <v>53</v>
       </c>
       <c r="C31">
         <v>989</v>
@@ -3940,7 +4098,7 @@
         <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="C32">
         <v>1027</v>
@@ -4011,7 +4169,7 @@
         <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>33</v>
+        <v>55</v>
       </c>
       <c r="C33">
         <v>966</v>
@@ -4082,7 +4240,7 @@
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>34</v>
+        <v>56</v>
       </c>
       <c r="C34">
         <v>913</v>
@@ -4153,7 +4311,7 @@
         <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>35</v>
+        <v>57</v>
       </c>
       <c r="C35">
         <v>439</v>
@@ -4224,7 +4382,7 @@
         <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>36</v>
+        <v>58</v>
       </c>
       <c r="C36">
         <v>1160</v>
@@ -4295,7 +4453,7 @@
         <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>37</v>
+        <v>59</v>
       </c>
       <c r="C37">
         <v>1115</v>
@@ -4366,7 +4524,7 @@
         <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="C38">
         <v>1162</v>
@@ -4437,7 +4595,7 @@
         <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>39</v>
+        <v>61</v>
       </c>
       <c r="C39">
         <v>753</v>
@@ -4508,7 +4666,7 @@
         <v>38</v>
       </c>
       <c r="B40" t="s">
-        <v>39</v>
+        <v>61</v>
       </c>
       <c r="C40">
         <v>917</v>
@@ -4579,7 +4737,7 @@
         <v>39</v>
       </c>
       <c r="B41" t="s">
-        <v>40</v>
+        <v>62</v>
       </c>
       <c r="C41">
         <v>927</v>
@@ -4650,7 +4808,7 @@
         <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>41</v>
+        <v>63</v>
       </c>
       <c r="C42">
         <v>723</v>
@@ -4721,7 +4879,7 @@
         <v>41</v>
       </c>
       <c r="B43" t="s">
-        <v>42</v>
+        <v>64</v>
       </c>
       <c r="C43">
         <v>1046</v>
@@ -4792,7 +4950,7 @@
         <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>43</v>
+        <v>65</v>
       </c>
       <c r="C44">
         <v>451</v>
@@ -4863,7 +5021,7 @@
         <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>44</v>
+        <v>66</v>
       </c>
       <c r="C45">
         <v>832</v>
@@ -4934,7 +5092,7 @@
         <v>44</v>
       </c>
       <c r="B46" t="s">
-        <v>45</v>
+        <v>67</v>
       </c>
       <c r="C46">
         <v>765</v>
@@ -5005,7 +5163,7 @@
         <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>46</v>
+        <v>68</v>
       </c>
       <c r="C47">
         <v>1223</v>
@@ -5076,7 +5234,7 @@
         <v>46</v>
       </c>
       <c r="B48" t="s">
-        <v>47</v>
+        <v>69</v>
       </c>
       <c r="C48">
         <v>849</v>
@@ -5147,7 +5305,7 @@
         <v>47</v>
       </c>
       <c r="B49" t="s">
-        <v>48</v>
+        <v>70</v>
       </c>
       <c r="C49">
         <v>718</v>
@@ -5218,7 +5376,7 @@
         <v>48</v>
       </c>
       <c r="B50" t="s">
-        <v>49</v>
+        <v>71</v>
       </c>
       <c r="C50">
         <v>1112</v>
@@ -5289,7 +5447,7 @@
         <v>49</v>
       </c>
       <c r="B51" t="s">
-        <v>50</v>
+        <v>72</v>
       </c>
       <c r="C51">
         <v>619</v>
@@ -5360,7 +5518,7 @@
         <v>50</v>
       </c>
       <c r="B52" t="s">
-        <v>51</v>
+        <v>73</v>
       </c>
       <c r="C52">
         <v>958</v>
@@ -5431,7 +5589,7 @@
         <v>51</v>
       </c>
       <c r="B53" t="s">
-        <v>52</v>
+        <v>74</v>
       </c>
       <c r="C53">
         <v>585</v>
@@ -5502,7 +5660,7 @@
         <v>52</v>
       </c>
       <c r="B54" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="C54">
         <v>781</v>
@@ -5573,7 +5731,7 @@
         <v>53</v>
       </c>
       <c r="B55" t="s">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="C55">
         <v>868</v>
@@ -5644,7 +5802,7 @@
         <v>54</v>
       </c>
       <c r="B56" t="s">
-        <v>55</v>
+        <v>77</v>
       </c>
       <c r="C56">
         <v>1073</v>
@@ -5715,7 +5873,7 @@
         <v>55</v>
       </c>
       <c r="B57" t="s">
-        <v>56</v>
+        <v>78</v>
       </c>
       <c r="C57">
         <v>676</v>
@@ -5786,7 +5944,7 @@
         <v>56</v>
       </c>
       <c r="B58" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="C58">
         <v>844</v>
@@ -5857,7 +6015,7 @@
         <v>57</v>
       </c>
       <c r="B59" t="s">
-        <v>58</v>
+        <v>80</v>
       </c>
       <c r="C59">
         <v>829</v>
@@ -5928,7 +6086,7 @@
         <v>58</v>
       </c>
       <c r="B60" t="s">
-        <v>59</v>
+        <v>81</v>
       </c>
       <c r="C60">
         <v>602</v>
@@ -5999,7 +6157,7 @@
         <v>59</v>
       </c>
       <c r="B61" t="s">
-        <v>60</v>
+        <v>82</v>
       </c>
       <c r="C61">
         <v>1015</v>
@@ -6070,7 +6228,7 @@
         <v>60</v>
       </c>
       <c r="B62" t="s">
-        <v>61</v>
+        <v>83</v>
       </c>
       <c r="C62">
         <v>723</v>
@@ -6141,7 +6299,7 @@
         <v>61</v>
       </c>
       <c r="B63" t="s">
-        <v>62</v>
+        <v>84</v>
       </c>
       <c r="C63">
         <v>1055</v>
@@ -6212,7 +6370,7 @@
         <v>62</v>
       </c>
       <c r="B64" t="s">
-        <v>63</v>
+        <v>85</v>
       </c>
       <c r="C64">
         <v>1096</v>
@@ -6283,7 +6441,7 @@
         <v>63</v>
       </c>
       <c r="B65" t="s">
-        <v>64</v>
+        <v>86</v>
       </c>
       <c r="C65">
         <v>1130</v>
@@ -6354,7 +6512,7 @@
         <v>64</v>
       </c>
       <c r="B66" t="s">
-        <v>65</v>
+        <v>87</v>
       </c>
       <c r="C66">
         <v>901</v>
@@ -6425,7 +6583,7 @@
         <v>65</v>
       </c>
       <c r="B67" t="s">
-        <v>66</v>
+        <v>88</v>
       </c>
       <c r="C67">
         <v>885</v>
@@ -6496,7 +6654,7 @@
         <v>66</v>
       </c>
       <c r="B68" t="s">
-        <v>67</v>
+        <v>89</v>
       </c>
       <c r="C68">
         <v>806</v>
@@ -6567,7 +6725,7 @@
         <v>67</v>
       </c>
       <c r="B69" t="s">
-        <v>68</v>
+        <v>90</v>
       </c>
       <c r="C69">
         <v>874</v>
@@ -6638,7 +6796,7 @@
         <v>68</v>
       </c>
       <c r="B70" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="C70">
         <v>1016</v>
@@ -6709,7 +6867,7 @@
         <v>69</v>
       </c>
       <c r="B71" t="s">
-        <v>70</v>
+        <v>92</v>
       </c>
       <c r="C71">
         <v>748</v>
@@ -6780,7 +6938,7 @@
         <v>70</v>
       </c>
       <c r="B72" t="s">
-        <v>71</v>
+        <v>93</v>
       </c>
       <c r="C72">
         <v>992</v>
@@ -6851,7 +7009,7 @@
         <v>71</v>
       </c>
       <c r="B73" t="s">
-        <v>72</v>
+        <v>94</v>
       </c>
       <c r="C73">
         <v>1144</v>
@@ -6922,7 +7080,7 @@
         <v>72</v>
       </c>
       <c r="B74" t="s">
-        <v>73</v>
+        <v>95</v>
       </c>
       <c r="C74">
         <v>1083</v>
@@ -6993,7 +7151,7 @@
         <v>73</v>
       </c>
       <c r="B75" t="s">
-        <v>74</v>
+        <v>96</v>
       </c>
       <c r="C75">
         <v>0</v>
@@ -7064,7 +7222,7 @@
         <v>74</v>
       </c>
       <c r="B76" t="s">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="C76">
         <v>983</v>
@@ -7135,7 +7293,7 @@
         <v>75</v>
       </c>
       <c r="B77" t="s">
-        <v>76</v>
+        <v>98</v>
       </c>
       <c r="C77">
         <v>928</v>
@@ -7206,7 +7364,7 @@
         <v>76</v>
       </c>
       <c r="B78" t="s">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="C78">
         <v>927</v>
@@ -7277,7 +7435,7 @@
         <v>77</v>
       </c>
       <c r="B79" t="s">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="C79">
         <v>863</v>
@@ -7348,7 +7506,7 @@
         <v>78</v>
       </c>
       <c r="B80" t="s">
-        <v>79</v>
+        <v>101</v>
       </c>
       <c r="C80">
         <v>969</v>
@@ -7419,7 +7577,7 @@
         <v>79</v>
       </c>
       <c r="B81" t="s">
-        <v>80</v>
+        <v>102</v>
       </c>
       <c r="C81">
         <v>765</v>
@@ -7490,7 +7648,7 @@
         <v>80</v>
       </c>
       <c r="B82" t="s">
-        <v>81</v>
+        <v>103</v>
       </c>
       <c r="C82">
         <v>612</v>
@@ -7561,7 +7719,7 @@
         <v>81</v>
       </c>
       <c r="B83" t="s">
-        <v>82</v>
+        <v>104</v>
       </c>
       <c r="C83">
         <v>881</v>
@@ -7632,7 +7790,7 @@
         <v>82</v>
       </c>
       <c r="B84" t="s">
-        <v>83</v>
+        <v>105</v>
       </c>
       <c r="C84">
         <v>1183</v>
@@ -7703,7 +7861,7 @@
         <v>83</v>
       </c>
       <c r="B85" t="s">
-        <v>84</v>
+        <v>106</v>
       </c>
       <c r="C85">
         <v>990</v>
@@ -7774,7 +7932,7 @@
         <v>84</v>
       </c>
       <c r="B86" t="s">
-        <v>85</v>
+        <v>107</v>
       </c>
       <c r="C86">
         <v>870</v>
@@ -7845,7 +8003,7 @@
         <v>85</v>
       </c>
       <c r="B87" t="s">
-        <v>86</v>
+        <v>108</v>
       </c>
       <c r="C87">
         <v>942</v>
@@ -7916,7 +8074,7 @@
         <v>86</v>
       </c>
       <c r="B88" t="s">
-        <v>87</v>
+        <v>109</v>
       </c>
       <c r="C88">
         <v>695</v>
@@ -7987,7 +8145,7 @@
         <v>87</v>
       </c>
       <c r="B89" t="s">
-        <v>88</v>
+        <v>110</v>
       </c>
       <c r="C89">
         <v>1089</v>
@@ -8058,7 +8216,7 @@
         <v>88</v>
       </c>
       <c r="B90" t="s">
-        <v>89</v>
+        <v>111</v>
       </c>
       <c r="C90">
         <v>881</v>
@@ -8129,7 +8287,7 @@
         <v>89</v>
       </c>
       <c r="B91" t="s">
-        <v>90</v>
+        <v>112</v>
       </c>
       <c r="C91">
         <v>889</v>
@@ -8200,7 +8358,7 @@
         <v>90</v>
       </c>
       <c r="B92" t="s">
-        <v>91</v>
+        <v>113</v>
       </c>
       <c r="C92">
         <v>621</v>
@@ -8271,7 +8429,7 @@
         <v>91</v>
       </c>
       <c r="B93" t="s">
-        <v>92</v>
+        <v>114</v>
       </c>
       <c r="C93">
         <v>580</v>
@@ -8342,7 +8500,7 @@
         <v>92</v>
       </c>
       <c r="B94" t="s">
-        <v>93</v>
+        <v>115</v>
       </c>
       <c r="C94">
         <v>725</v>
@@ -8413,7 +8571,7 @@
         <v>93</v>
       </c>
       <c r="B95" t="s">
-        <v>94</v>
+        <v>116</v>
       </c>
       <c r="C95">
         <v>660</v>
@@ -8484,7 +8642,7 @@
         <v>94</v>
       </c>
       <c r="B96" t="s">
-        <v>95</v>
+        <v>117</v>
       </c>
       <c r="C96">
         <v>777</v>
@@ -8555,7 +8713,7 @@
         <v>95</v>
       </c>
       <c r="B97" t="s">
-        <v>96</v>
+        <v>118</v>
       </c>
       <c r="C97">
         <v>771</v>
@@ -8626,7 +8784,7 @@
         <v>96</v>
       </c>
       <c r="B98" t="s">
-        <v>97</v>
+        <v>119</v>
       </c>
       <c r="C98">
         <v>585</v>
@@ -8697,7 +8855,7 @@
         <v>97</v>
       </c>
       <c r="B99" t="s">
-        <v>98</v>
+        <v>120</v>
       </c>
       <c r="C99">
         <v>620</v>
@@ -8768,7 +8926,7 @@
         <v>98</v>
       </c>
       <c r="B100" t="s">
-        <v>99</v>
+        <v>121</v>
       </c>
       <c r="C100">
         <v>907</v>
@@ -8839,7 +8997,7 @@
         <v>99</v>
       </c>
       <c r="B101" t="s">
-        <v>100</v>
+        <v>122</v>
       </c>
       <c r="C101">
         <v>953</v>
@@ -8910,7 +9068,7 @@
         <v>100</v>
       </c>
       <c r="B102" t="s">
-        <v>101</v>
+        <v>123</v>
       </c>
       <c r="C102">
         <v>526</v>
@@ -8981,7 +9139,7 @@
         <v>101</v>
       </c>
       <c r="B103" t="s">
-        <v>102</v>
+        <v>124</v>
       </c>
       <c r="C103">
         <v>868</v>
@@ -9052,7 +9210,7 @@
         <v>102</v>
       </c>
       <c r="B104" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="C104">
         <v>768</v>
@@ -9123,7 +9281,7 @@
         <v>103</v>
       </c>
       <c r="B105" t="s">
-        <v>104</v>
+        <v>126</v>
       </c>
       <c r="C105">
         <v>736</v>
@@ -9194,7 +9352,7 @@
         <v>104</v>
       </c>
       <c r="B106" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="C106">
         <v>535</v>
@@ -9265,7 +9423,7 @@
         <v>105</v>
       </c>
       <c r="B107" t="s">
-        <v>106</v>
+        <v>128</v>
       </c>
       <c r="C107">
         <v>855</v>
@@ -9336,7 +9494,7 @@
         <v>106</v>
       </c>
       <c r="B108" t="s">
-        <v>107</v>
+        <v>129</v>
       </c>
       <c r="C108">
         <v>962</v>
@@ -9407,7 +9565,7 @@
         <v>107</v>
       </c>
       <c r="B109" t="s">
-        <v>108</v>
+        <v>130</v>
       </c>
       <c r="C109">
         <v>1004</v>
@@ -9478,7 +9636,7 @@
         <v>108</v>
       </c>
       <c r="B110" t="s">
-        <v>109</v>
+        <v>131</v>
       </c>
       <c r="C110">
         <v>837</v>
@@ -9549,7 +9707,7 @@
         <v>109</v>
       </c>
       <c r="B111" t="s">
-        <v>110</v>
+        <v>132</v>
       </c>
       <c r="C111">
         <v>844</v>
@@ -9620,7 +9778,7 @@
         <v>110</v>
       </c>
       <c r="B112" t="s">
-        <v>111</v>
+        <v>133</v>
       </c>
       <c r="C112">
         <v>940</v>
@@ -9691,7 +9849,7 @@
         <v>111</v>
       </c>
       <c r="B113" t="s">
-        <v>112</v>
+        <v>134</v>
       </c>
       <c r="C113">
         <v>782</v>
@@ -9762,7 +9920,7 @@
         <v>112</v>
       </c>
       <c r="B114" t="s">
-        <v>113</v>
+        <v>135</v>
       </c>
       <c r="C114">
         <v>993</v>
@@ -9833,7 +9991,7 @@
         <v>113</v>
       </c>
       <c r="B115" t="s">
-        <v>114</v>
+        <v>136</v>
       </c>
       <c r="C115">
         <v>608</v>
@@ -9904,7 +10062,7 @@
         <v>114</v>
       </c>
       <c r="B116" t="s">
-        <v>115</v>
+        <v>137</v>
       </c>
       <c r="C116">
         <v>594</v>
@@ -9975,7 +10133,7 @@
         <v>115</v>
       </c>
       <c r="B117" t="s">
-        <v>116</v>
+        <v>138</v>
       </c>
       <c r="C117">
         <v>727</v>
@@ -10046,7 +10204,7 @@
         <v>116</v>
       </c>
       <c r="B118" t="s">
-        <v>117</v>
+        <v>139</v>
       </c>
       <c r="C118">
         <v>878</v>
@@ -10117,7 +10275,7 @@
         <v>117</v>
       </c>
       <c r="B119" t="s">
-        <v>118</v>
+        <v>140</v>
       </c>
       <c r="C119">
         <v>873</v>
@@ -10188,7 +10346,7 @@
         <v>118</v>
       </c>
       <c r="B120" t="s">
-        <v>119</v>
+        <v>141</v>
       </c>
       <c r="C120">
         <v>788</v>
@@ -10259,7 +10417,7 @@
         <v>119</v>
       </c>
       <c r="B121" t="s">
-        <v>120</v>
+        <v>142</v>
       </c>
       <c r="C121">
         <v>523</v>
@@ -10330,7 +10488,7 @@
         <v>120</v>
       </c>
       <c r="B122" t="s">
-        <v>121</v>
+        <v>143</v>
       </c>
       <c r="C122">
         <v>1199</v>
@@ -10401,7 +10559,7 @@
         <v>121</v>
       </c>
       <c r="B123" t="s">
-        <v>122</v>
+        <v>144</v>
       </c>
       <c r="C123">
         <v>842</v>
@@ -10472,7 +10630,7 @@
         <v>122</v>
       </c>
       <c r="B124" t="s">
-        <v>123</v>
+        <v>145</v>
       </c>
       <c r="C124">
         <v>1190</v>
@@ -10543,7 +10701,7 @@
         <v>123</v>
       </c>
       <c r="B125" t="s">
-        <v>124</v>
+        <v>146</v>
       </c>
       <c r="C125">
         <v>788</v>
@@ -10614,7 +10772,7 @@
         <v>124</v>
       </c>
       <c r="B126" t="s">
-        <v>125</v>
+        <v>147</v>
       </c>
       <c r="C126">
         <v>746</v>
@@ -10685,7 +10843,7 @@
         <v>125</v>
       </c>
       <c r="B127" t="s">
-        <v>126</v>
+        <v>148</v>
       </c>
       <c r="C127">
         <v>681</v>
@@ -10756,7 +10914,7 @@
         <v>126</v>
       </c>
       <c r="B128" t="s">
-        <v>127</v>
+        <v>149</v>
       </c>
       <c r="C128">
         <v>816</v>
@@ -10827,7 +10985,7 @@
         <v>127</v>
       </c>
       <c r="B129" t="s">
-        <v>128</v>
+        <v>150</v>
       </c>
       <c r="C129">
         <v>537</v>
@@ -10898,7 +11056,7 @@
         <v>128</v>
       </c>
       <c r="B130" t="s">
-        <v>129</v>
+        <v>151</v>
       </c>
       <c r="C130">
         <v>998</v>
@@ -10969,7 +11127,7 @@
         <v>129</v>
       </c>
       <c r="B131" t="s">
-        <v>130</v>
+        <v>152</v>
       </c>
       <c r="C131">
         <v>820</v>
@@ -11040,7 +11198,7 @@
         <v>130</v>
       </c>
       <c r="B132" t="s">
-        <v>131</v>
+        <v>153</v>
       </c>
       <c r="C132">
         <v>785</v>
@@ -11111,7 +11269,7 @@
         <v>131</v>
       </c>
       <c r="B133" t="s">
-        <v>132</v>
+        <v>154</v>
       </c>
       <c r="C133">
         <v>552</v>
@@ -11182,7 +11340,7 @@
         <v>132</v>
       </c>
       <c r="B134" t="s">
-        <v>133</v>
+        <v>155</v>
       </c>
       <c r="C134">
         <v>1007</v>
@@ -11253,7 +11411,7 @@
         <v>133</v>
       </c>
       <c r="B135" t="s">
-        <v>134</v>
+        <v>156</v>
       </c>
       <c r="C135">
         <v>802</v>
@@ -11324,7 +11482,7 @@
         <v>134</v>
       </c>
       <c r="B136" t="s">
-        <v>135</v>
+        <v>157</v>
       </c>
       <c r="C136">
         <v>853</v>
@@ -11395,7 +11553,7 @@
         <v>135</v>
       </c>
       <c r="B137" t="s">
-        <v>136</v>
+        <v>158</v>
       </c>
       <c r="C137">
         <v>769</v>
@@ -11466,7 +11624,7 @@
         <v>136</v>
       </c>
       <c r="B138" t="s">
-        <v>137</v>
+        <v>159</v>
       </c>
       <c r="C138">
         <v>724</v>
@@ -11537,7 +11695,7 @@
         <v>137</v>
       </c>
       <c r="B139" t="s">
-        <v>138</v>
+        <v>160</v>
       </c>
       <c r="C139">
         <v>655</v>
@@ -11608,7 +11766,7 @@
         <v>138</v>
       </c>
       <c r="B140" t="s">
-        <v>139</v>
+        <v>161</v>
       </c>
       <c r="C140">
         <v>688</v>
@@ -11679,7 +11837,7 @@
         <v>139</v>
       </c>
       <c r="B141" t="s">
-        <v>140</v>
+        <v>162</v>
       </c>
       <c r="C141">
         <v>0</v>
@@ -11750,7 +11908,7 @@
         <v>140</v>
       </c>
       <c r="B142" t="s">
-        <v>141</v>
+        <v>163</v>
       </c>
       <c r="C142">
         <v>1013</v>
@@ -11821,7 +11979,7 @@
         <v>141</v>
       </c>
       <c r="B143" t="s">
-        <v>142</v>
+        <v>164</v>
       </c>
       <c r="C143">
         <v>941</v>
@@ -11892,7 +12050,7 @@
         <v>142</v>
       </c>
       <c r="B144" t="s">
-        <v>143</v>
+        <v>165</v>
       </c>
       <c r="C144">
         <v>897</v>
@@ -11963,7 +12121,7 @@
         <v>143</v>
       </c>
       <c r="B145" t="s">
-        <v>144</v>
+        <v>166</v>
       </c>
       <c r="C145">
         <v>611</v>
@@ -12034,7 +12192,7 @@
         <v>144</v>
       </c>
       <c r="B146" t="s">
-        <v>145</v>
+        <v>167</v>
       </c>
       <c r="C146">
         <v>768</v>
@@ -12105,7 +12263,7 @@
         <v>145</v>
       </c>
       <c r="B147" t="s">
-        <v>145</v>
+        <v>167</v>
       </c>
       <c r="C147">
         <v>1004</v>
@@ -12176,7 +12334,7 @@
         <v>146</v>
       </c>
       <c r="B148" t="s">
-        <v>145</v>
+        <v>167</v>
       </c>
       <c r="C148">
         <v>1081</v>
@@ -12247,7 +12405,7 @@
         <v>147</v>
       </c>
       <c r="B149" t="s">
-        <v>146</v>
+        <v>168</v>
       </c>
       <c r="C149">
         <v>707</v>
@@ -12318,7 +12476,7 @@
         <v>148</v>
       </c>
       <c r="B150" t="s">
-        <v>147</v>
+        <v>169</v>
       </c>
       <c r="C150">
         <v>766</v>
@@ -12389,7 +12547,7 @@
         <v>149</v>
       </c>
       <c r="B151" t="s">
-        <v>148</v>
+        <v>170</v>
       </c>
       <c r="C151">
         <v>895</v>
@@ -12460,7 +12618,7 @@
         <v>150</v>
       </c>
       <c r="B152" t="s">
-        <v>149</v>
+        <v>171</v>
       </c>
       <c r="C152">
         <v>1069</v>
@@ -12531,7 +12689,7 @@
         <v>151</v>
       </c>
       <c r="B153" t="s">
-        <v>150</v>
+        <v>172</v>
       </c>
       <c r="C153">
         <v>843</v>
@@ -12602,7 +12760,7 @@
         <v>152</v>
       </c>
       <c r="B154" t="s">
-        <v>151</v>
+        <v>173</v>
       </c>
       <c r="C154">
         <v>1102</v>
@@ -12673,7 +12831,7 @@
         <v>153</v>
       </c>
       <c r="B155" t="s">
-        <v>152</v>
+        <v>174</v>
       </c>
       <c r="C155">
         <v>829</v>
@@ -12744,7 +12902,7 @@
         <v>154</v>
       </c>
       <c r="B156" t="s">
-        <v>153</v>
+        <v>175</v>
       </c>
       <c r="C156">
         <v>895</v>
@@ -12815,7 +12973,7 @@
         <v>155</v>
       </c>
       <c r="B157" t="s">
-        <v>154</v>
+        <v>176</v>
       </c>
       <c r="C157">
         <v>612</v>
@@ -12886,7 +13044,7 @@
         <v>156</v>
       </c>
       <c r="B158" t="s">
-        <v>155</v>
+        <v>177</v>
       </c>
       <c r="C158">
         <v>695</v>
@@ -12957,7 +13115,7 @@
         <v>157</v>
       </c>
       <c r="B159" t="s">
-        <v>156</v>
+        <v>178</v>
       </c>
       <c r="C159">
         <v>1002</v>
@@ -13028,7 +13186,7 @@
         <v>158</v>
       </c>
       <c r="B160" t="s">
-        <v>157</v>
+        <v>179</v>
       </c>
       <c r="C160">
         <v>890</v>
@@ -13099,7 +13257,7 @@
         <v>159</v>
       </c>
       <c r="B161" t="s">
-        <v>158</v>
+        <v>180</v>
       </c>
       <c r="C161">
         <v>1060</v>
@@ -13170,7 +13328,7 @@
         <v>160</v>
       </c>
       <c r="B162" t="s">
-        <v>159</v>
+        <v>181</v>
       </c>
       <c r="C162">
         <v>697</v>
@@ -13241,7 +13399,7 @@
         <v>161</v>
       </c>
       <c r="B163" t="s">
-        <v>160</v>
+        <v>182</v>
       </c>
       <c r="C163">
         <v>680</v>
@@ -13312,7 +13470,7 @@
         <v>162</v>
       </c>
       <c r="B164" t="s">
-        <v>161</v>
+        <v>183</v>
       </c>
       <c r="C164">
         <v>745</v>
@@ -13383,7 +13541,7 @@
         <v>163</v>
       </c>
       <c r="B165" t="s">
-        <v>162</v>
+        <v>184</v>
       </c>
       <c r="C165">
         <v>985</v>
@@ -13454,7 +13612,7 @@
         <v>164</v>
       </c>
       <c r="B166" t="s">
-        <v>163</v>
+        <v>185</v>
       </c>
       <c r="C166">
         <v>699</v>
@@ -13525,7 +13683,7 @@
         <v>165</v>
       </c>
       <c r="B167" t="s">
-        <v>164</v>
+        <v>186</v>
       </c>
       <c r="C167">
         <v>625</v>
@@ -13596,7 +13754,7 @@
         <v>166</v>
       </c>
       <c r="B168" t="s">
-        <v>165</v>
+        <v>187</v>
       </c>
       <c r="C168">
         <v>780</v>
@@ -13667,7 +13825,7 @@
         <v>167</v>
       </c>
       <c r="B169" t="s">
-        <v>166</v>
+        <v>188</v>
       </c>
       <c r="C169">
         <v>734</v>
@@ -13738,7 +13896,7 @@
         <v>168</v>
       </c>
       <c r="B170" t="s">
-        <v>167</v>
+        <v>189</v>
       </c>
       <c r="C170">
         <v>907</v>
@@ -13809,7 +13967,7 @@
         <v>169</v>
       </c>
       <c r="B171" t="s">
-        <v>168</v>
+        <v>190</v>
       </c>
       <c r="C171">
         <v>434</v>
@@ -13880,7 +14038,7 @@
         <v>170</v>
       </c>
       <c r="B172" t="s">
-        <v>169</v>
+        <v>191</v>
       </c>
       <c r="C172">
         <v>1247</v>
@@ -13951,7 +14109,7 @@
         <v>171</v>
       </c>
       <c r="B173" t="s">
-        <v>170</v>
+        <v>192</v>
       </c>
       <c r="C173">
         <v>722</v>
@@ -14022,7 +14180,7 @@
         <v>172</v>
       </c>
       <c r="B174" t="s">
-        <v>171</v>
+        <v>193</v>
       </c>
       <c r="C174">
         <v>741</v>
@@ -14093,7 +14251,7 @@
         <v>173</v>
       </c>
       <c r="B175" t="s">
-        <v>172</v>
+        <v>194</v>
       </c>
       <c r="C175">
         <v>954</v>
@@ -14164,7 +14322,7 @@
         <v>174</v>
       </c>
       <c r="B176" t="s">
-        <v>173</v>
+        <v>195</v>
       </c>
       <c r="C176">
         <v>865</v>
@@ -14235,7 +14393,7 @@
         <v>175</v>
       </c>
       <c r="B177" t="s">
-        <v>174</v>
+        <v>196</v>
       </c>
       <c r="C177">
         <v>712</v>
@@ -14306,7 +14464,7 @@
         <v>176</v>
       </c>
       <c r="B178" t="s">
-        <v>175</v>
+        <v>197</v>
       </c>
       <c r="C178">
         <v>960</v>
@@ -14377,7 +14535,7 @@
         <v>177</v>
       </c>
       <c r="B179" t="s">
-        <v>176</v>
+        <v>198</v>
       </c>
       <c r="C179">
         <v>1118</v>
@@ -14448,7 +14606,7 @@
         <v>178</v>
       </c>
       <c r="B180" t="s">
-        <v>177</v>
+        <v>199</v>
       </c>
       <c r="C180">
         <v>673</v>
@@ -14519,7 +14677,7 @@
         <v>179</v>
       </c>
       <c r="B181" t="s">
-        <v>178</v>
+        <v>200</v>
       </c>
       <c r="C181">
         <v>561</v>
@@ -14590,7 +14748,7 @@
         <v>180</v>
       </c>
       <c r="B182" t="s">
-        <v>179</v>
+        <v>201</v>
       </c>
       <c r="C182">
         <v>815</v>
@@ -14661,7 +14819,7 @@
         <v>181</v>
       </c>
       <c r="B183" t="s">
-        <v>180</v>
+        <v>202</v>
       </c>
       <c r="C183">
         <v>967</v>
@@ -14732,7 +14890,7 @@
         <v>182</v>
       </c>
       <c r="B184" t="s">
-        <v>181</v>
+        <v>203</v>
       </c>
       <c r="C184">
         <v>1197</v>
@@ -14803,7 +14961,7 @@
         <v>183</v>
       </c>
       <c r="B185" t="s">
-        <v>182</v>
+        <v>204</v>
       </c>
       <c r="C185">
         <v>1023</v>
@@ -14874,7 +15032,7 @@
         <v>184</v>
       </c>
       <c r="B186" t="s">
-        <v>183</v>
+        <v>205</v>
       </c>
       <c r="C186">
         <v>965</v>
@@ -14945,7 +15103,7 @@
         <v>185</v>
       </c>
       <c r="B187" t="s">
-        <v>184</v>
+        <v>206</v>
       </c>
       <c r="C187">
         <v>1027</v>
@@ -15016,7 +15174,7 @@
         <v>186</v>
       </c>
       <c r="B188" t="s">
-        <v>185</v>
+        <v>207</v>
       </c>
       <c r="C188">
         <v>769</v>
@@ -15087,7 +15245,7 @@
         <v>187</v>
       </c>
       <c r="B189" t="s">
-        <v>186</v>
+        <v>208</v>
       </c>
       <c r="C189">
         <v>1009</v>
@@ -15158,7 +15316,7 @@
         <v>188</v>
       </c>
       <c r="B190" t="s">
-        <v>187</v>
+        <v>209</v>
       </c>
       <c r="C190">
         <v>800</v>
@@ -15229,7 +15387,7 @@
         <v>189</v>
       </c>
       <c r="B191" t="s">
-        <v>188</v>
+        <v>210</v>
       </c>
       <c r="C191">
         <v>918</v>
@@ -15300,7 +15458,7 @@
         <v>190</v>
       </c>
       <c r="B192" t="s">
-        <v>189</v>
+        <v>211</v>
       </c>
       <c r="C192">
         <v>967</v>
@@ -15371,7 +15529,7 @@
         <v>191</v>
       </c>
       <c r="B193" t="s">
-        <v>190</v>
+        <v>212</v>
       </c>
       <c r="C193">
         <v>789</v>
@@ -15442,7 +15600,7 @@
         <v>192</v>
       </c>
       <c r="B194" t="s">
-        <v>191</v>
+        <v>213</v>
       </c>
       <c r="C194">
         <v>966</v>
@@ -15513,7 +15671,7 @@
         <v>193</v>
       </c>
       <c r="B195" t="s">
-        <v>192</v>
+        <v>214</v>
       </c>
       <c r="C195">
         <v>952</v>
@@ -15584,7 +15742,7 @@
         <v>194</v>
       </c>
       <c r="B196" t="s">
-        <v>193</v>
+        <v>215</v>
       </c>
       <c r="C196">
         <v>910</v>
@@ -15655,7 +15813,7 @@
         <v>195</v>
       </c>
       <c r="B197" t="s">
-        <v>194</v>
+        <v>216</v>
       </c>
       <c r="C197">
         <v>820</v>
@@ -15726,7 +15884,7 @@
         <v>196</v>
       </c>
       <c r="B198" t="s">
-        <v>195</v>
+        <v>217</v>
       </c>
       <c r="C198">
         <v>1178</v>
@@ -15797,7 +15955,7 @@
         <v>197</v>
       </c>
       <c r="B199" t="s">
-        <v>196</v>
+        <v>218</v>
       </c>
       <c r="C199">
         <v>1209</v>
@@ -15868,7 +16026,7 @@
         <v>198</v>
       </c>
       <c r="B200" t="s">
-        <v>197</v>
+        <v>219</v>
       </c>
       <c r="C200">
         <v>685</v>
@@ -15939,7 +16097,7 @@
         <v>199</v>
       </c>
       <c r="B201" t="s">
-        <v>198</v>
+        <v>220</v>
       </c>
       <c r="C201">
         <v>688</v>
@@ -16010,7 +16168,7 @@
         <v>200</v>
       </c>
       <c r="B202" t="s">
-        <v>199</v>
+        <v>221</v>
       </c>
       <c r="C202">
         <v>719</v>
@@ -16081,7 +16239,7 @@
         <v>201</v>
       </c>
       <c r="B203" t="s">
-        <v>200</v>
+        <v>222</v>
       </c>
       <c r="C203">
         <v>744</v>
@@ -16152,7 +16310,7 @@
         <v>202</v>
       </c>
       <c r="B204" t="s">
-        <v>201</v>
+        <v>223</v>
       </c>
       <c r="C204">
         <v>1007</v>
@@ -16223,7 +16381,7 @@
         <v>203</v>
       </c>
       <c r="B205" t="s">
-        <v>202</v>
+        <v>224</v>
       </c>
       <c r="C205">
         <v>817</v>
@@ -16294,7 +16452,7 @@
         <v>204</v>
       </c>
       <c r="B206" t="s">
-        <v>203</v>
+        <v>225</v>
       </c>
       <c r="C206">
         <v>491</v>
@@ -16365,7 +16523,7 @@
         <v>205</v>
       </c>
       <c r="B207" t="s">
-        <v>204</v>
+        <v>226</v>
       </c>
       <c r="C207">
         <v>569</v>
@@ -16436,7 +16594,7 @@
         <v>206</v>
       </c>
       <c r="B208" t="s">
-        <v>205</v>
+        <v>227</v>
       </c>
       <c r="C208">
         <v>778</v>
@@ -16507,7 +16665,7 @@
         <v>207</v>
       </c>
       <c r="B209" t="s">
-        <v>206</v>
+        <v>228</v>
       </c>
       <c r="C209">
         <v>806</v>
@@ -16578,7 +16736,7 @@
         <v>208</v>
       </c>
       <c r="B210" t="s">
-        <v>207</v>
+        <v>229</v>
       </c>
       <c r="C210">
         <v>704</v>
@@ -16649,7 +16807,7 @@
         <v>209</v>
       </c>
       <c r="B211" t="s">
-        <v>208</v>
+        <v>230</v>
       </c>
       <c r="C211">
         <v>1022</v>
@@ -16720,7 +16878,7 @@
         <v>210</v>
       </c>
       <c r="B212" t="s">
-        <v>209</v>
+        <v>231</v>
       </c>
       <c r="C212">
         <v>800</v>
@@ -16791,7 +16949,7 @@
         <v>211</v>
       </c>
       <c r="B213" t="s">
-        <v>210</v>
+        <v>232</v>
       </c>
       <c r="C213">
         <v>740</v>
@@ -16862,7 +17020,7 @@
         <v>212</v>
       </c>
       <c r="B214" t="s">
-        <v>211</v>
+        <v>233</v>
       </c>
       <c r="C214">
         <v>673</v>
@@ -16933,7 +17091,7 @@
         <v>213</v>
       </c>
       <c r="B215" t="s">
-        <v>212</v>
+        <v>234</v>
       </c>
       <c r="C215">
         <v>686</v>
@@ -17004,7 +17162,7 @@
         <v>214</v>
       </c>
       <c r="B216" t="s">
-        <v>213</v>
+        <v>235</v>
       </c>
       <c r="C216">
         <v>971</v>
@@ -17075,7 +17233,7 @@
         <v>215</v>
       </c>
       <c r="B217" t="s">
-        <v>214</v>
+        <v>236</v>
       </c>
       <c r="C217">
         <v>986</v>
@@ -17146,7 +17304,7 @@
         <v>216</v>
       </c>
       <c r="B218" t="s">
-        <v>215</v>
+        <v>237</v>
       </c>
       <c r="C218">
         <v>584</v>
@@ -17217,7 +17375,7 @@
         <v>217</v>
       </c>
       <c r="B219" t="s">
-        <v>216</v>
+        <v>238</v>
       </c>
       <c r="C219">
         <v>715</v>
@@ -17288,7 +17446,7 @@
         <v>218</v>
       </c>
       <c r="B220" t="s">
-        <v>217</v>
+        <v>239</v>
       </c>
       <c r="C220">
         <v>605</v>
@@ -17359,7 +17517,7 @@
         <v>219</v>
       </c>
       <c r="B221" t="s">
-        <v>218</v>
+        <v>240</v>
       </c>
       <c r="C221">
         <v>703</v>
@@ -17430,7 +17588,7 @@
         <v>220</v>
       </c>
       <c r="B222" t="s">
-        <v>219</v>
+        <v>241</v>
       </c>
       <c r="C222">
         <v>704</v>
@@ -17501,7 +17659,7 @@
         <v>221</v>
       </c>
       <c r="B223" t="s">
-        <v>220</v>
+        <v>242</v>
       </c>
       <c r="C223">
         <v>718</v>
@@ -17572,7 +17730,7 @@
         <v>222</v>
       </c>
       <c r="B224" t="s">
-        <v>221</v>
+        <v>243</v>
       </c>
       <c r="C224">
         <v>681</v>
@@ -17643,7 +17801,7 @@
         <v>223</v>
       </c>
       <c r="B225" t="s">
-        <v>222</v>
+        <v>244</v>
       </c>
       <c r="C225">
         <v>776</v>
@@ -17714,7 +17872,7 @@
         <v>224</v>
       </c>
       <c r="B226" t="s">
-        <v>223</v>
+        <v>245</v>
       </c>
       <c r="C226">
         <v>713</v>
@@ -17785,7 +17943,7 @@
         <v>225</v>
       </c>
       <c r="B227" t="s">
-        <v>224</v>
+        <v>246</v>
       </c>
       <c r="C227">
         <v>1149</v>
@@ -17856,7 +18014,7 @@
         <v>226</v>
       </c>
       <c r="B228" t="s">
-        <v>225</v>
+        <v>247</v>
       </c>
       <c r="C228">
         <v>929</v>
@@ -17927,7 +18085,7 @@
         <v>227</v>
       </c>
       <c r="B229" t="s">
-        <v>226</v>
+        <v>248</v>
       </c>
       <c r="C229">
         <v>802</v>
@@ -17998,7 +18156,7 @@
         <v>228</v>
       </c>
       <c r="B230" t="s">
-        <v>227</v>
+        <v>249</v>
       </c>
       <c r="C230">
         <v>560</v>
@@ -18069,7 +18227,7 @@
         <v>229</v>
       </c>
       <c r="B231" t="s">
-        <v>228</v>
+        <v>250</v>
       </c>
       <c r="C231">
         <v>988</v>
@@ -18140,7 +18298,7 @@
         <v>230</v>
       </c>
       <c r="B232" t="s">
-        <v>229</v>
+        <v>251</v>
       </c>
       <c r="C232">
         <v>1013</v>
@@ -18211,7 +18369,7 @@
         <v>231</v>
       </c>
       <c r="B233" t="s">
-        <v>230</v>
+        <v>252</v>
       </c>
       <c r="C233">
         <v>949</v>
@@ -18282,7 +18440,7 @@
         <v>232</v>
       </c>
       <c r="B234" t="s">
-        <v>231</v>
+        <v>253</v>
       </c>
       <c r="C234">
         <v>671</v>
@@ -18353,7 +18511,7 @@
         <v>233</v>
       </c>
       <c r="B235" t="s">
-        <v>232</v>
+        <v>254</v>
       </c>
       <c r="C235">
         <v>728</v>
@@ -18424,7 +18582,7 @@
         <v>234</v>
       </c>
       <c r="B236" t="s">
-        <v>233</v>
+        <v>255</v>
       </c>
       <c r="C236">
         <v>607</v>
@@ -18495,7 +18653,7 @@
         <v>235</v>
       </c>
       <c r="B237" t="s">
-        <v>234</v>
+        <v>256</v>
       </c>
       <c r="C237">
         <v>820</v>
@@ -18566,7 +18724,7 @@
         <v>236</v>
       </c>
       <c r="B238" t="s">
-        <v>235</v>
+        <v>257</v>
       </c>
       <c r="C238">
         <v>1068</v>
@@ -18637,7 +18795,7 @@
         <v>237</v>
       </c>
       <c r="B239" t="s">
-        <v>236</v>
+        <v>258</v>
       </c>
       <c r="C239">
         <v>973</v>
@@ -18708,7 +18866,7 @@
         <v>238</v>
       </c>
       <c r="B240" t="s">
-        <v>237</v>
+        <v>259</v>
       </c>
       <c r="C240">
         <v>1097</v>
@@ -18779,7 +18937,7 @@
         <v>239</v>
       </c>
       <c r="B241" t="s">
-        <v>238</v>
+        <v>260</v>
       </c>
       <c r="C241">
         <v>1168</v>
@@ -18850,7 +19008,7 @@
         <v>240</v>
       </c>
       <c r="B242" t="s">
-        <v>239</v>
+        <v>261</v>
       </c>
       <c r="C242">
         <v>356</v>
@@ -18921,7 +19079,7 @@
         <v>241</v>
       </c>
       <c r="B243" t="s">
-        <v>240</v>
+        <v>262</v>
       </c>
       <c r="C243">
         <v>1002</v>
@@ -18992,7 +19150,7 @@
         <v>242</v>
       </c>
       <c r="B244" t="s">
-        <v>241</v>
+        <v>263</v>
       </c>
       <c r="C244">
         <v>597</v>
@@ -19063,7 +19221,7 @@
         <v>243</v>
       </c>
       <c r="B245" t="s">
-        <v>242</v>
+        <v>264</v>
       </c>
       <c r="C245">
         <v>691</v>
@@ -19134,7 +19292,7 @@
         <v>244</v>
       </c>
       <c r="B246" t="s">
-        <v>243</v>
+        <v>265</v>
       </c>
       <c r="C246">
         <v>1032</v>
@@ -19205,7 +19363,7 @@
         <v>245</v>
       </c>
       <c r="B247" t="s">
-        <v>244</v>
+        <v>266</v>
       </c>
       <c r="C247">
         <v>858</v>
@@ -19276,7 +19434,7 @@
         <v>246</v>
       </c>
       <c r="B248" t="s">
-        <v>245</v>
+        <v>267</v>
       </c>
       <c r="C248">
         <v>653</v>
@@ -19347,7 +19505,7 @@
         <v>247</v>
       </c>
       <c r="B249" t="s">
-        <v>246</v>
+        <v>268</v>
       </c>
       <c r="C249">
         <v>743</v>
@@ -19418,7 +19576,7 @@
         <v>248</v>
       </c>
       <c r="B250" t="s">
-        <v>247</v>
+        <v>269</v>
       </c>
       <c r="C250">
         <v>539</v>
@@ -19489,7 +19647,7 @@
         <v>249</v>
       </c>
       <c r="B251" t="s">
-        <v>248</v>
+        <v>270</v>
       </c>
       <c r="C251">
         <v>1145</v>
@@ -19560,7 +19718,7 @@
         <v>250</v>
       </c>
       <c r="B252" t="s">
-        <v>249</v>
+        <v>271</v>
       </c>
       <c r="C252">
         <v>963</v>
@@ -19631,7 +19789,7 @@
         <v>251</v>
       </c>
       <c r="B253" t="s">
-        <v>250</v>
+        <v>272</v>
       </c>
       <c r="C253">
         <v>691</v>
@@ -19702,7 +19860,7 @@
         <v>252</v>
       </c>
       <c r="B254" t="s">
-        <v>251</v>
+        <v>273</v>
       </c>
       <c r="C254">
         <v>647</v>
@@ -19773,7 +19931,7 @@
         <v>253</v>
       </c>
       <c r="B255" t="s">
-        <v>252</v>
+        <v>274</v>
       </c>
       <c r="C255">
         <v>616</v>
@@ -19844,7 +20002,7 @@
         <v>254</v>
       </c>
       <c r="B256" t="s">
-        <v>253</v>
+        <v>275</v>
       </c>
       <c r="C256">
         <v>984</v>
@@ -19915,7 +20073,7 @@
         <v>255</v>
       </c>
       <c r="B257" t="s">
-        <v>254</v>
+        <v>276</v>
       </c>
       <c r="C257">
         <v>530</v>
@@ -19986,7 +20144,7 @@
         <v>256</v>
       </c>
       <c r="B258" t="s">
-        <v>255</v>
+        <v>277</v>
       </c>
       <c r="C258">
         <v>1002</v>
@@ -20057,7 +20215,7 @@
         <v>257</v>
       </c>
       <c r="B259" t="s">
-        <v>256</v>
+        <v>278</v>
       </c>
       <c r="C259">
         <v>651</v>
@@ -20128,7 +20286,7 @@
         <v>258</v>
       </c>
       <c r="B260" t="s">
-        <v>257</v>
+        <v>279</v>
       </c>
       <c r="C260">
         <v>610</v>
@@ -20199,7 +20357,7 @@
         <v>259</v>
       </c>
       <c r="B261" t="s">
-        <v>258</v>
+        <v>280</v>
       </c>
       <c r="C261">
         <v>552</v>
@@ -20270,7 +20428,7 @@
         <v>260</v>
       </c>
       <c r="B262" t="s">
-        <v>259</v>
+        <v>281</v>
       </c>
       <c r="C262">
         <v>669</v>
@@ -20341,7 +20499,7 @@
         <v>261</v>
       </c>
       <c r="B263" t="s">
-        <v>260</v>
+        <v>282</v>
       </c>
       <c r="C263">
         <v>1069</v>
@@ -20412,7 +20570,7 @@
         <v>262</v>
       </c>
       <c r="B264" t="s">
-        <v>261</v>
+        <v>283</v>
       </c>
       <c r="C264">
         <v>588</v>
@@ -20483,7 +20641,7 @@
         <v>263</v>
       </c>
       <c r="B265" t="s">
-        <v>262</v>
+        <v>284</v>
       </c>
       <c r="C265">
         <v>649</v>
@@ -20554,7 +20712,7 @@
         <v>264</v>
       </c>
       <c r="B266" t="s">
-        <v>263</v>
+        <v>285</v>
       </c>
       <c r="C266">
         <v>1128</v>
@@ -20625,7 +20783,7 @@
         <v>265</v>
       </c>
       <c r="B267" t="s">
-        <v>264</v>
+        <v>286</v>
       </c>
       <c r="C267">
         <v>846</v>
@@ -20696,7 +20854,7 @@
         <v>266</v>
       </c>
       <c r="B268" t="s">
-        <v>265</v>
+        <v>287</v>
       </c>
       <c r="C268">
         <v>1182</v>
@@ -20767,7 +20925,7 @@
         <v>267</v>
       </c>
       <c r="B269" t="s">
-        <v>266</v>
+        <v>288</v>
       </c>
       <c r="C269">
         <v>715</v>
@@ -20838,7 +20996,7 @@
         <v>268</v>
       </c>
       <c r="B270" t="s">
-        <v>267</v>
+        <v>289</v>
       </c>
       <c r="C270">
         <v>1116</v>
@@ -20909,7 +21067,7 @@
         <v>269</v>
       </c>
       <c r="B271" t="s">
-        <v>268</v>
+        <v>290</v>
       </c>
       <c r="C271">
         <v>1141</v>
@@ -20980,7 +21138,7 @@
         <v>270</v>
       </c>
       <c r="B272" t="s">
-        <v>269</v>
+        <v>291</v>
       </c>
       <c r="C272">
         <v>1164</v>
@@ -21051,7 +21209,7 @@
         <v>271</v>
       </c>
       <c r="B273" t="s">
-        <v>270</v>
+        <v>292</v>
       </c>
       <c r="C273">
         <v>745</v>
@@ -21122,7 +21280,7 @@
         <v>272</v>
       </c>
       <c r="B274" t="s">
-        <v>271</v>
+        <v>293</v>
       </c>
       <c r="C274">
         <v>845</v>
@@ -21193,7 +21351,7 @@
         <v>273</v>
       </c>
       <c r="B275" t="s">
-        <v>272</v>
+        <v>294</v>
       </c>
       <c r="C275">
         <v>719</v>
@@ -21264,7 +21422,7 @@
         <v>274</v>
       </c>
       <c r="B276" t="s">
-        <v>273</v>
+        <v>295</v>
       </c>
       <c r="C276">
         <v>800</v>
@@ -21335,7 +21493,7 @@
         <v>275</v>
       </c>
       <c r="B277" t="s">
-        <v>274</v>
+        <v>296</v>
       </c>
       <c r="C277">
         <v>667</v>
@@ -21406,7 +21564,7 @@
         <v>276</v>
       </c>
       <c r="B278" t="s">
-        <v>275</v>
+        <v>297</v>
       </c>
       <c r="C278">
         <v>814</v>
@@ -21477,7 +21635,7 @@
         <v>277</v>
       </c>
       <c r="B279" t="s">
-        <v>276</v>
+        <v>298</v>
       </c>
       <c r="C279">
         <v>971</v>
@@ -21548,7 +21706,7 @@
         <v>278</v>
       </c>
       <c r="B280" t="s">
-        <v>277</v>
+        <v>299</v>
       </c>
       <c r="C280">
         <v>839</v>
@@ -21619,7 +21777,7 @@
         <v>279</v>
       </c>
       <c r="B281" t="s">
-        <v>278</v>
+        <v>300</v>
       </c>
       <c r="C281">
         <v>853</v>
@@ -21690,7 +21848,7 @@
         <v>280</v>
       </c>
       <c r="B282" t="s">
-        <v>279</v>
+        <v>301</v>
       </c>
       <c r="C282">
         <v>769</v>
@@ -21761,7 +21919,7 @@
         <v>281</v>
       </c>
       <c r="B283" t="s">
-        <v>280</v>
+        <v>302</v>
       </c>
       <c r="C283">
         <v>595</v>
@@ -21832,7 +21990,7 @@
         <v>282</v>
       </c>
       <c r="B284" t="s">
-        <v>281</v>
+        <v>303</v>
       </c>
       <c r="C284">
         <v>862</v>
@@ -21903,7 +22061,7 @@
         <v>283</v>
       </c>
       <c r="B285" t="s">
-        <v>282</v>
+        <v>304</v>
       </c>
       <c r="C285">
         <v>1048</v>
@@ -21974,7 +22132,7 @@
         <v>284</v>
       </c>
       <c r="B286" t="s">
-        <v>283</v>
+        <v>305</v>
       </c>
       <c r="C286">
         <v>728</v>
@@ -22045,7 +22203,7 @@
         <v>285</v>
       </c>
       <c r="B287" t="s">
-        <v>284</v>
+        <v>306</v>
       </c>
       <c r="C287">
         <v>712</v>
@@ -22116,7 +22274,7 @@
         <v>286</v>
       </c>
       <c r="B288" t="s">
-        <v>285</v>
+        <v>307</v>
       </c>
       <c r="C288">
         <v>544</v>
@@ -22187,7 +22345,7 @@
         <v>287</v>
       </c>
       <c r="B289" t="s">
-        <v>286</v>
+        <v>308</v>
       </c>
       <c r="C289">
         <v>730</v>
@@ -22258,7 +22416,7 @@
         <v>288</v>
       </c>
       <c r="B290" t="s">
-        <v>287</v>
+        <v>309</v>
       </c>
       <c r="C290">
         <v>578</v>
@@ -22329,7 +22487,7 @@
         <v>289</v>
       </c>
       <c r="B291" t="s">
-        <v>288</v>
+        <v>310</v>
       </c>
       <c r="C291">
         <v>789</v>
@@ -22400,7 +22558,7 @@
         <v>290</v>
       </c>
       <c r="B292" t="s">
-        <v>289</v>
+        <v>311</v>
       </c>
       <c r="C292">
         <v>713</v>
@@ -22471,7 +22629,7 @@
         <v>291</v>
       </c>
       <c r="B293" t="s">
-        <v>290</v>
+        <v>312</v>
       </c>
       <c r="C293">
         <v>737</v>
@@ -22542,7 +22700,7 @@
         <v>292</v>
       </c>
       <c r="B294" t="s">
-        <v>291</v>
+        <v>313</v>
       </c>
       <c r="C294">
         <v>1087</v>
@@ -22613,7 +22771,7 @@
         <v>293</v>
       </c>
       <c r="B295" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="C295">
         <v>762</v>
@@ -22684,7 +22842,7 @@
         <v>294</v>
       </c>
       <c r="B296" t="s">
-        <v>293</v>
+        <v>315</v>
       </c>
       <c r="C296">
         <v>795</v>
@@ -22755,7 +22913,7 @@
         <v>295</v>
       </c>
       <c r="B297" t="s">
-        <v>294</v>
+        <v>316</v>
       </c>
       <c r="C297">
         <v>600</v>
@@ -22826,7 +22984,7 @@
         <v>296</v>
       </c>
       <c r="B298" t="s">
-        <v>295</v>
+        <v>317</v>
       </c>
       <c r="C298">
         <v>776</v>
@@ -22897,7 +23055,7 @@
         <v>297</v>
       </c>
       <c r="B299" t="s">
-        <v>296</v>
+        <v>318</v>
       </c>
       <c r="C299">
         <v>1015</v>
@@ -22968,7 +23126,7 @@
         <v>298</v>
       </c>
       <c r="B300" t="s">
-        <v>297</v>
+        <v>319</v>
       </c>
       <c r="C300">
         <v>521</v>
@@ -23039,7 +23197,7 @@
         <v>299</v>
       </c>
       <c r="B301" t="s">
-        <v>298</v>
+        <v>320</v>
       </c>
       <c r="C301">
         <v>614</v>
@@ -23110,7 +23268,7 @@
         <v>300</v>
       </c>
       <c r="B302" t="s">
-        <v>299</v>
+        <v>321</v>
       </c>
       <c r="C302">
         <v>642</v>
@@ -23181,7 +23339,7 @@
         <v>301</v>
       </c>
       <c r="B303" t="s">
-        <v>300</v>
+        <v>322</v>
       </c>
       <c r="C303">
         <v>620</v>
@@ -23252,7 +23410,7 @@
         <v>302</v>
       </c>
       <c r="B304" t="s">
-        <v>301</v>
+        <v>323</v>
       </c>
       <c r="C304">
         <v>863</v>
@@ -23323,7 +23481,7 @@
         <v>303</v>
       </c>
       <c r="B305" t="s">
-        <v>302</v>
+        <v>324</v>
       </c>
       <c r="C305">
         <v>896</v>
@@ -23394,7 +23552,7 @@
         <v>304</v>
       </c>
       <c r="B306" t="s">
-        <v>303</v>
+        <v>325</v>
       </c>
       <c r="C306">
         <v>1022</v>
@@ -23465,7 +23623,7 @@
         <v>305</v>
       </c>
       <c r="B307" t="s">
-        <v>304</v>
+        <v>326</v>
       </c>
       <c r="C307">
         <v>792</v>
@@ -23536,7 +23694,7 @@
         <v>306</v>
       </c>
       <c r="B308" t="s">
-        <v>305</v>
+        <v>327</v>
       </c>
       <c r="C308">
         <v>652</v>
@@ -23607,7 +23765,7 @@
         <v>307</v>
       </c>
       <c r="B309" t="s">
-        <v>306</v>
+        <v>328</v>
       </c>
       <c r="C309">
         <v>628</v>
@@ -23678,7 +23836,7 @@
         <v>308</v>
       </c>
       <c r="B310" t="s">
-        <v>307</v>
+        <v>329</v>
       </c>
       <c r="C310">
         <v>879</v>
@@ -23749,7 +23907,7 @@
         <v>309</v>
       </c>
       <c r="B311" t="s">
-        <v>308</v>
+        <v>330</v>
       </c>
       <c r="C311">
         <v>885</v>
@@ -23820,7 +23978,7 @@
         <v>310</v>
       </c>
       <c r="B312" t="s">
-        <v>309</v>
+        <v>331</v>
       </c>
       <c r="C312">
         <v>436</v>
@@ -23891,7 +24049,7 @@
         <v>311</v>
       </c>
       <c r="B313" t="s">
-        <v>310</v>
+        <v>332</v>
       </c>
       <c r="C313">
         <v>799</v>
@@ -23962,7 +24120,7 @@
         <v>312</v>
       </c>
       <c r="B314" t="s">
-        <v>311</v>
+        <v>333</v>
       </c>
       <c r="C314">
         <v>1196</v>
@@ -24033,7 +24191,7 @@
         <v>313</v>
       </c>
       <c r="B315" t="s">
-        <v>312</v>
+        <v>334</v>
       </c>
       <c r="C315">
         <v>425</v>
@@ -24104,7 +24262,7 @@
         <v>314</v>
       </c>
       <c r="B316" t="s">
-        <v>313</v>
+        <v>335</v>
       </c>
       <c r="C316">
         <v>824</v>
@@ -24175,7 +24333,7 @@
         <v>315</v>
       </c>
       <c r="B317" t="s">
-        <v>314</v>
+        <v>336</v>
       </c>
       <c r="C317">
         <v>1005</v>
@@ -24246,7 +24404,7 @@
         <v>316</v>
       </c>
       <c r="B318" t="s">
-        <v>315</v>
+        <v>337</v>
       </c>
       <c r="C318">
         <v>1070</v>
@@ -24317,7 +24475,7 @@
         <v>317</v>
       </c>
       <c r="B319" t="s">
-        <v>316</v>
+        <v>338</v>
       </c>
       <c r="C319">
         <v>977</v>
@@ -24388,7 +24546,7 @@
         <v>318</v>
       </c>
       <c r="B320" t="s">
-        <v>317</v>
+        <v>339</v>
       </c>
       <c r="C320">
         <v>1101</v>
@@ -24459,7 +24617,7 @@
         <v>319</v>
       </c>
       <c r="B321" t="s">
-        <v>318</v>
+        <v>340</v>
       </c>
       <c r="C321">
         <v>629</v>
@@ -24530,7 +24688,7 @@
         <v>320</v>
       </c>
       <c r="B322" t="s">
-        <v>319</v>
+        <v>341</v>
       </c>
       <c r="C322">
         <v>643</v>
@@ -24601,7 +24759,7 @@
         <v>321</v>
       </c>
       <c r="B323" t="s">
-        <v>320</v>
+        <v>342</v>
       </c>
       <c r="C323">
         <v>798</v>
@@ -24672,7 +24830,7 @@
         <v>322</v>
       </c>
       <c r="B324" t="s">
-        <v>321</v>
+        <v>343</v>
       </c>
       <c r="C324">
         <v>1179</v>
@@ -24743,7 +24901,7 @@
         <v>323</v>
       </c>
       <c r="B325" t="s">
-        <v>322</v>
+        <v>344</v>
       </c>
       <c r="C325">
         <v>1026</v>
@@ -24814,7 +24972,7 @@
         <v>324</v>
       </c>
       <c r="B326" t="s">
-        <v>323</v>
+        <v>345</v>
       </c>
       <c r="C326">
         <v>486</v>
@@ -24885,7 +25043,7 @@
         <v>325</v>
       </c>
       <c r="B327" t="s">
-        <v>324</v>
+        <v>346</v>
       </c>
       <c r="C327">
         <v>1148</v>
@@ -24956,7 +25114,7 @@
         <v>326</v>
       </c>
       <c r="B328" t="s">
-        <v>325</v>
+        <v>347</v>
       </c>
       <c r="C328">
         <v>811</v>
@@ -25027,7 +25185,7 @@
         <v>327</v>
       </c>
       <c r="B329" t="s">
-        <v>326</v>
+        <v>348</v>
       </c>
       <c r="C329">
         <v>738</v>
@@ -25098,7 +25256,7 @@
         <v>328</v>
       </c>
       <c r="B330" t="s">
-        <v>327</v>
+        <v>349</v>
       </c>
       <c r="C330">
         <v>508</v>
@@ -25169,7 +25327,7 @@
         <v>329</v>
       </c>
       <c r="B331" t="s">
-        <v>328</v>
+        <v>350</v>
       </c>
       <c r="C331">
         <v>650</v>
@@ -25240,7 +25398,7 @@
         <v>330</v>
       </c>
       <c r="B332" t="s">
-        <v>329</v>
+        <v>351</v>
       </c>
       <c r="C332">
         <v>610</v>
@@ -25311,7 +25469,7 @@
         <v>331</v>
       </c>
       <c r="B333" t="s">
-        <v>330</v>
+        <v>352</v>
       </c>
       <c r="C333">
         <v>1192</v>
@@ -25382,7 +25540,7 @@
         <v>332</v>
       </c>
       <c r="B334" t="s">
-        <v>331</v>
+        <v>353</v>
       </c>
       <c r="C334">
         <v>615</v>
@@ -25453,7 +25611,7 @@
         <v>333</v>
       </c>
       <c r="B335" t="s">
-        <v>332</v>
+        <v>354</v>
       </c>
       <c r="C335">
         <v>1004</v>
@@ -25524,7 +25682,7 @@
         <v>334</v>
       </c>
       <c r="B336" t="s">
-        <v>333</v>
+        <v>355</v>
       </c>
       <c r="C336">
         <v>896</v>
@@ -25595,7 +25753,7 @@
         <v>335</v>
       </c>
       <c r="B337" t="s">
-        <v>334</v>
+        <v>356</v>
       </c>
       <c r="C337">
         <v>924</v>
@@ -25666,7 +25824,7 @@
         <v>336</v>
       </c>
       <c r="B338" t="s">
-        <v>335</v>
+        <v>357</v>
       </c>
       <c r="C338">
         <v>1041</v>
@@ -25737,7 +25895,7 @@
         <v>337</v>
       </c>
       <c r="B339" t="s">
-        <v>336</v>
+        <v>358</v>
       </c>
       <c r="C339">
         <v>477</v>
@@ -25808,7 +25966,7 @@
         <v>338</v>
       </c>
       <c r="B340" t="s">
-        <v>337</v>
+        <v>359</v>
       </c>
       <c r="C340">
         <v>793</v>
@@ -25879,7 +26037,7 @@
         <v>339</v>
       </c>
       <c r="B341" t="s">
-        <v>338</v>
+        <v>360</v>
       </c>
       <c r="C341">
         <v>818</v>
@@ -25950,7 +26108,7 @@
         <v>340</v>
       </c>
       <c r="B342" t="s">
-        <v>339</v>
+        <v>361</v>
       </c>
       <c r="C342">
         <v>938</v>
@@ -26021,7 +26179,7 @@
         <v>341</v>
       </c>
       <c r="B343" t="s">
-        <v>340</v>
+        <v>362</v>
       </c>
       <c r="C343">
         <v>657</v>
@@ -26092,7 +26250,7 @@
         <v>342</v>
       </c>
       <c r="B344" t="s">
-        <v>341</v>
+        <v>363</v>
       </c>
       <c r="C344">
         <v>949</v>
@@ -26163,7 +26321,7 @@
         <v>343</v>
       </c>
       <c r="B345" t="s">
-        <v>342</v>
+        <v>364</v>
       </c>
       <c r="C345">
         <v>1130</v>
@@ -26234,7 +26392,7 @@
         <v>344</v>
       </c>
       <c r="B346" t="s">
-        <v>343</v>
+        <v>365</v>
       </c>
       <c r="C346">
         <v>1194</v>
@@ -26305,7 +26463,7 @@
         <v>345</v>
       </c>
       <c r="B347" t="s">
-        <v>344</v>
+        <v>366</v>
       </c>
       <c r="C347">
         <v>1087</v>
@@ -26376,7 +26534,7 @@
         <v>346</v>
       </c>
       <c r="B348" t="s">
-        <v>345</v>
+        <v>367</v>
       </c>
       <c r="C348">
         <v>974</v>
@@ -26447,7 +26605,7 @@
         <v>347</v>
       </c>
       <c r="B349" t="s">
-        <v>346</v>
+        <v>368</v>
       </c>
       <c r="C349">
         <v>881</v>
@@ -26518,7 +26676,7 @@
         <v>348</v>
       </c>
       <c r="B350" t="s">
-        <v>347</v>
+        <v>369</v>
       </c>
       <c r="C350">
         <v>1194</v>
@@ -26589,7 +26747,7 @@
         <v>349</v>
       </c>
       <c r="B351" t="s">
-        <v>348</v>
+        <v>370</v>
       </c>
       <c r="C351">
         <v>1202</v>
@@ -26660,7 +26818,7 @@
         <v>350</v>
       </c>
       <c r="B352" t="s">
-        <v>349</v>
+        <v>371</v>
       </c>
       <c r="C352">
         <v>827</v>
@@ -26731,7 +26889,7 @@
         <v>351</v>
       </c>
       <c r="B353" t="s">
-        <v>350</v>
+        <v>372</v>
       </c>
       <c r="C353">
         <v>824</v>
@@ -26802,7 +26960,7 @@
         <v>352</v>
       </c>
       <c r="B354" t="s">
-        <v>351</v>
+        <v>373</v>
       </c>
       <c r="C354">
         <v>950</v>
@@ -26873,7 +27031,7 @@
         <v>353</v>
       </c>
       <c r="B355" t="s">
-        <v>352</v>
+        <v>374</v>
       </c>
       <c r="C355">
         <v>699</v>
@@ -26944,7 +27102,7 @@
         <v>354</v>
       </c>
       <c r="B356" t="s">
-        <v>353</v>
+        <v>375</v>
       </c>
       <c r="C356">
         <v>624</v>
@@ -27015,7 +27173,7 @@
         <v>355</v>
       </c>
       <c r="B357" t="s">
-        <v>354</v>
+        <v>376</v>
       </c>
       <c r="C357">
         <v>1010</v>
@@ -27086,7 +27244,7 @@
         <v>356</v>
       </c>
       <c r="B358" t="s">
-        <v>355</v>
+        <v>377</v>
       </c>
       <c r="C358">
         <v>838</v>
@@ -27157,7 +27315,7 @@
         <v>357</v>
       </c>
       <c r="B359" t="s">
-        <v>356</v>
+        <v>378</v>
       </c>
       <c r="C359">
         <v>856</v>
@@ -27228,7 +27386,7 @@
         <v>358</v>
       </c>
       <c r="B360" t="s">
-        <v>357</v>
+        <v>379</v>
       </c>
       <c r="C360">
         <v>691</v>
@@ -27299,7 +27457,7 @@
         <v>359</v>
       </c>
       <c r="B361" t="s">
-        <v>358</v>
+        <v>380</v>
       </c>
       <c r="C361">
         <v>768</v>
@@ -27370,7 +27528,7 @@
         <v>360</v>
       </c>
       <c r="B362" t="s">
-        <v>359</v>
+        <v>381</v>
       </c>
       <c r="C362">
         <v>1052</v>
@@ -27441,7 +27599,7 @@
         <v>361</v>
       </c>
       <c r="B363" t="s">
-        <v>360</v>
+        <v>382</v>
       </c>
       <c r="C363">
         <v>846</v>
@@ -27512,7 +27670,7 @@
         <v>362</v>
       </c>
       <c r="B364" t="s">
-        <v>361</v>
+        <v>383</v>
       </c>
       <c r="C364">
         <v>734</v>
@@ -27583,7 +27741,7 @@
         <v>363</v>
       </c>
       <c r="B365" t="s">
-        <v>362</v>
+        <v>384</v>
       </c>
       <c r="C365">
         <v>1208</v>
@@ -27654,7 +27812,7 @@
         <v>364</v>
       </c>
       <c r="B366" t="s">
-        <v>363</v>
+        <v>385</v>
       </c>
       <c r="C366">
         <v>718</v>
@@ -27725,7 +27883,7 @@
         <v>365</v>
       </c>
       <c r="B367" t="s">
-        <v>364</v>
+        <v>386</v>
       </c>
       <c r="C367">
         <v>1048</v>
@@ -27796,7 +27954,7 @@
         <v>366</v>
       </c>
       <c r="B368" t="s">
-        <v>365</v>
+        <v>387</v>
       </c>
       <c r="C368">
         <v>638</v>
@@ -27867,7 +28025,7 @@
         <v>367</v>
       </c>
       <c r="B369" t="s">
-        <v>366</v>
+        <v>388</v>
       </c>
       <c r="C369">
         <v>995</v>
@@ -27938,7 +28096,7 @@
         <v>368</v>
       </c>
       <c r="B370" t="s">
-        <v>367</v>
+        <v>389</v>
       </c>
       <c r="C370">
         <v>855</v>
@@ -28009,7 +28167,7 @@
         <v>369</v>
       </c>
       <c r="B371" t="s">
-        <v>368</v>
+        <v>390</v>
       </c>
       <c r="C371">
         <v>1180</v>
@@ -28080,7 +28238,7 @@
         <v>370</v>
       </c>
       <c r="B372" t="s">
-        <v>369</v>
+        <v>391</v>
       </c>
       <c r="C372">
         <v>1152</v>
@@ -28151,7 +28309,7 @@
         <v>371</v>
       </c>
       <c r="B373" t="s">
-        <v>370</v>
+        <v>392</v>
       </c>
       <c r="C373">
         <v>621</v>
@@ -28222,7 +28380,7 @@
         <v>372</v>
       </c>
       <c r="B374" t="s">
-        <v>371</v>
+        <v>393</v>
       </c>
       <c r="C374">
         <v>891</v>
@@ -28293,7 +28451,7 @@
         <v>373</v>
       </c>
       <c r="B375" t="s">
-        <v>372</v>
+        <v>394</v>
       </c>
       <c r="C375">
         <v>1180</v>
@@ -28364,7 +28522,7 @@
         <v>374</v>
       </c>
       <c r="B376" t="s">
-        <v>373</v>
+        <v>395</v>
       </c>
       <c r="C376">
         <v>1031</v>
@@ -28435,7 +28593,7 @@
         <v>375</v>
       </c>
       <c r="B377" t="s">
-        <v>374</v>
+        <v>396</v>
       </c>
       <c r="C377">
         <v>1190</v>
@@ -28506,7 +28664,7 @@
         <v>376</v>
       </c>
       <c r="B378" t="s">
-        <v>375</v>
+        <v>397</v>
       </c>
       <c r="C378">
         <v>923</v>
@@ -28577,7 +28735,7 @@
         <v>377</v>
       </c>
       <c r="B379" t="s">
-        <v>376</v>
+        <v>398</v>
       </c>
       <c r="C379">
         <v>948</v>
@@ -28648,7 +28806,7 @@
         <v>378</v>
       </c>
       <c r="B380" t="s">
-        <v>377</v>
+        <v>399</v>
       </c>
       <c r="C380">
         <v>536</v>
@@ -28719,7 +28877,7 @@
         <v>379</v>
       </c>
       <c r="B381" t="s">
-        <v>378</v>
+        <v>400</v>
       </c>
       <c r="C381">
         <v>1178</v>
@@ -28790,7 +28948,7 @@
         <v>380</v>
       </c>
       <c r="B382" t="s">
-        <v>379</v>
+        <v>401</v>
       </c>
       <c r="C382">
         <v>797</v>
@@ -28861,7 +29019,7 @@
         <v>381</v>
       </c>
       <c r="B383" t="s">
-        <v>380</v>
+        <v>402</v>
       </c>
       <c r="C383">
         <v>692</v>
@@ -28932,7 +29090,7 @@
         <v>382</v>
       </c>
       <c r="B384" t="s">
-        <v>381</v>
+        <v>403</v>
       </c>
       <c r="C384">
         <v>938</v>
@@ -29003,7 +29161,7 @@
         <v>383</v>
       </c>
       <c r="B385" t="s">
-        <v>382</v>
+        <v>404</v>
       </c>
       <c r="C385">
         <v>819</v>
@@ -29074,7 +29232,7 @@
         <v>384</v>
       </c>
       <c r="B386" t="s">
-        <v>383</v>
+        <v>405</v>
       </c>
       <c r="C386">
         <v>742</v>
@@ -29145,7 +29303,7 @@
         <v>385</v>
       </c>
       <c r="B387" t="s">
-        <v>384</v>
+        <v>406</v>
       </c>
       <c r="C387">
         <v>940</v>
@@ -29216,7 +29374,7 @@
         <v>386</v>
       </c>
       <c r="B388" t="s">
-        <v>385</v>
+        <v>407</v>
       </c>
       <c r="C388">
         <v>472</v>
@@ -29287,7 +29445,7 @@
         <v>387</v>
       </c>
       <c r="B389" t="s">
-        <v>386</v>
+        <v>408</v>
       </c>
       <c r="C389">
         <v>1075</v>
@@ -29358,7 +29516,7 @@
         <v>388</v>
       </c>
       <c r="B390" t="s">
-        <v>387</v>
+        <v>409</v>
       </c>
       <c r="C390">
         <v>1078</v>
@@ -29429,7 +29587,7 @@
         <v>389</v>
       </c>
       <c r="B391" t="s">
-        <v>388</v>
+        <v>410</v>
       </c>
       <c r="C391">
         <v>1039</v>
@@ -29500,7 +29658,7 @@
         <v>390</v>
       </c>
       <c r="B392" t="s">
-        <v>389</v>
+        <v>411</v>
       </c>
       <c r="C392">
         <v>876</v>
@@ -29571,7 +29729,7 @@
         <v>391</v>
       </c>
       <c r="B393" t="s">
-        <v>390</v>
+        <v>412</v>
       </c>
       <c r="C393">
         <v>878</v>
@@ -29642,7 +29800,7 @@
         <v>392</v>
       </c>
       <c r="B394" t="s">
-        <v>391</v>
+        <v>413</v>
       </c>
       <c r="C394">
         <v>701</v>
@@ -29713,7 +29871,7 @@
         <v>393</v>
       </c>
       <c r="B395" t="s">
-        <v>392</v>
+        <v>414</v>
       </c>
       <c r="C395">
         <v>606</v>
@@ -29784,7 +29942,7 @@
         <v>394</v>
       </c>
       <c r="B396" t="s">
-        <v>393</v>
+        <v>415</v>
       </c>
       <c r="C396">
         <v>635</v>
@@ -29855,7 +30013,7 @@
         <v>395</v>
       </c>
       <c r="B397" t="s">
-        <v>394</v>
+        <v>416</v>
       </c>
       <c r="C397">
         <v>826</v>
@@ -29926,7 +30084,7 @@
         <v>396</v>
       </c>
       <c r="B398" t="s">
-        <v>395</v>
+        <v>417</v>
       </c>
       <c r="C398">
         <v>715</v>
@@ -29997,7 +30155,7 @@
         <v>397</v>
       </c>
       <c r="B399" t="s">
-        <v>396</v>
+        <v>418</v>
       </c>
       <c r="C399">
         <v>691</v>
@@ -30068,7 +30226,7 @@
         <v>398</v>
       </c>
       <c r="B400" t="s">
-        <v>397</v>
+        <v>419</v>
       </c>
       <c r="C400">
         <v>613</v>
@@ -30139,7 +30297,7 @@
         <v>399</v>
       </c>
       <c r="B401" t="s">
-        <v>398</v>
+        <v>420</v>
       </c>
       <c r="C401">
         <v>663</v>
@@ -30210,7 +30368,7 @@
         <v>400</v>
       </c>
       <c r="B402" t="s">
-        <v>399</v>
+        <v>421</v>
       </c>
       <c r="C402">
         <v>850</v>
@@ -30281,7 +30439,7 @@
         <v>401</v>
       </c>
       <c r="B403" t="s">
-        <v>400</v>
+        <v>422</v>
       </c>
       <c r="C403">
         <v>797</v>
@@ -30352,7 +30510,7 @@
         <v>402</v>
       </c>
       <c r="B404" t="s">
-        <v>401</v>
+        <v>423</v>
       </c>
       <c r="C404">
         <v>764</v>
@@ -30423,7 +30581,7 @@
         <v>403</v>
       </c>
       <c r="B405" t="s">
-        <v>402</v>
+        <v>424</v>
       </c>
       <c r="C405">
         <v>923</v>
@@ -30494,7 +30652,7 @@
         <v>404</v>
       </c>
       <c r="B406" t="s">
-        <v>403</v>
+        <v>425</v>
       </c>
       <c r="C406">
         <v>814</v>
@@ -30565,7 +30723,7 @@
         <v>405</v>
       </c>
       <c r="B407" t="s">
-        <v>404</v>
+        <v>426</v>
       </c>
       <c r="C407">
         <v>660</v>
@@ -30636,7 +30794,7 @@
         <v>406</v>
       </c>
       <c r="B408" t="s">
-        <v>405</v>
+        <v>427</v>
       </c>
       <c r="C408">
         <v>804</v>
@@ -30707,7 +30865,7 @@
         <v>407</v>
       </c>
       <c r="B409" t="s">
-        <v>406</v>
+        <v>428</v>
       </c>
       <c r="C409">
         <v>888</v>
@@ -30778,7 +30936,7 @@
         <v>408</v>
       </c>
       <c r="B410" t="s">
-        <v>407</v>
+        <v>429</v>
       </c>
       <c r="C410">
         <v>642</v>
@@ -30849,7 +31007,7 @@
         <v>409</v>
       </c>
       <c r="B411" t="s">
-        <v>408</v>
+        <v>430</v>
       </c>
       <c r="C411">
         <v>466</v>
@@ -30920,7 +31078,7 @@
         <v>410</v>
       </c>
       <c r="B412" t="s">
-        <v>409</v>
+        <v>431</v>
       </c>
       <c r="C412">
         <v>975</v>
@@ -30991,7 +31149,7 @@
         <v>411</v>
       </c>
       <c r="B413" t="s">
-        <v>410</v>
+        <v>432</v>
       </c>
       <c r="C413">
         <v>749</v>
@@ -31062,7 +31220,7 @@
         <v>412</v>
       </c>
       <c r="B414" t="s">
-        <v>411</v>
+        <v>433</v>
       </c>
       <c r="C414">
         <v>584</v>
@@ -31133,7 +31291,7 @@
         <v>413</v>
       </c>
       <c r="B415" t="s">
-        <v>412</v>
+        <v>434</v>
       </c>
       <c r="C415">
         <v>885</v>
@@ -31204,7 +31362,7 @@
         <v>414</v>
       </c>
       <c r="B416" t="s">
-        <v>413</v>
+        <v>435</v>
       </c>
       <c r="C416">
         <v>738</v>
@@ -31275,7 +31433,7 @@
         <v>415</v>
       </c>
       <c r="B417" t="s">
-        <v>414</v>
+        <v>436</v>
       </c>
       <c r="C417">
         <v>677</v>
@@ -31346,7 +31504,7 @@
         <v>416</v>
       </c>
       <c r="B418" t="s">
-        <v>415</v>
+        <v>437</v>
       </c>
       <c r="C418">
         <v>746</v>
@@ -31417,7 +31575,7 @@
         <v>417</v>
       </c>
       <c r="B419" t="s">
-        <v>416</v>
+        <v>438</v>
       </c>
       <c r="C419">
         <v>627</v>
@@ -31488,7 +31646,7 @@
         <v>418</v>
       </c>
       <c r="B420" t="s">
-        <v>417</v>
+        <v>439</v>
       </c>
       <c r="C420">
         <v>719</v>
@@ -31559,7 +31717,7 @@
         <v>419</v>
       </c>
       <c r="B421" t="s">
-        <v>418</v>
+        <v>440</v>
       </c>
       <c r="C421">
         <v>772</v>
@@ -31630,7 +31788,7 @@
         <v>420</v>
       </c>
       <c r="B422" t="s">
-        <v>419</v>
+        <v>441</v>
       </c>
       <c r="C422">
         <v>946</v>
@@ -31701,7 +31859,7 @@
         <v>421</v>
       </c>
       <c r="B423" t="s">
-        <v>420</v>
+        <v>442</v>
       </c>
       <c r="C423">
         <v>883</v>
@@ -31772,7 +31930,7 @@
         <v>422</v>
       </c>
       <c r="B424" t="s">
-        <v>421</v>
+        <v>443</v>
       </c>
       <c r="C424">
         <v>1068</v>
@@ -31843,7 +32001,7 @@
         <v>423</v>
       </c>
       <c r="B425" t="s">
-        <v>422</v>
+        <v>444</v>
       </c>
       <c r="C425">
         <v>1117</v>
@@ -31914,7 +32072,7 @@
         <v>424</v>
       </c>
       <c r="B426" t="s">
-        <v>423</v>
+        <v>445</v>
       </c>
       <c r="C426">
         <v>805</v>
@@ -31985,7 +32143,7 @@
         <v>425</v>
       </c>
       <c r="B427" t="s">
-        <v>424</v>
+        <v>446</v>
       </c>
       <c r="C427">
         <v>579</v>
@@ -32056,7 +32214,7 @@
         <v>426</v>
       </c>
       <c r="B428" t="s">
-        <v>425</v>
+        <v>447</v>
       </c>
       <c r="C428">
         <v>1168</v>
@@ -32127,7 +32285,7 @@
         <v>427</v>
       </c>
       <c r="B429" t="s">
-        <v>426</v>
+        <v>448</v>
       </c>
       <c r="C429">
         <v>1163</v>
@@ -32198,7 +32356,7 @@
         <v>428</v>
       </c>
       <c r="B430" t="s">
-        <v>427</v>
+        <v>449</v>
       </c>
       <c r="C430">
         <v>649</v>
@@ -32269,7 +32427,7 @@
         <v>429</v>
       </c>
       <c r="B431" t="s">
-        <v>428</v>
+        <v>450</v>
       </c>
       <c r="C431">
         <v>557</v>
@@ -32340,7 +32498,7 @@
         <v>430</v>
       </c>
       <c r="B432" t="s">
-        <v>429</v>
+        <v>451</v>
       </c>
       <c r="C432">
         <v>814</v>
@@ -32411,7 +32569,7 @@
         <v>431</v>
       </c>
       <c r="B433" t="s">
-        <v>430</v>
+        <v>452</v>
       </c>
       <c r="C433">
         <v>643</v>
@@ -32482,7 +32640,7 @@
         <v>432</v>
       </c>
       <c r="B434" t="s">
-        <v>431</v>
+        <v>453</v>
       </c>
       <c r="C434">
         <v>959</v>
@@ -32553,7 +32711,7 @@
         <v>433</v>
       </c>
       <c r="B435" t="s">
-        <v>432</v>
+        <v>454</v>
       </c>
       <c r="C435">
         <v>955</v>
@@ -32624,7 +32782,7 @@
         <v>434</v>
       </c>
       <c r="B436" t="s">
-        <v>433</v>
+        <v>455</v>
       </c>
       <c r="C436">
         <v>906</v>
@@ -32695,7 +32853,7 @@
         <v>435</v>
       </c>
       <c r="B437" t="s">
-        <v>434</v>
+        <v>456</v>
       </c>
       <c r="C437">
         <v>748</v>
@@ -32766,7 +32924,7 @@
         <v>436</v>
       </c>
       <c r="B438" t="s">
-        <v>435</v>
+        <v>457</v>
       </c>
       <c r="C438">
         <v>790</v>
@@ -32837,7 +32995,7 @@
         <v>437</v>
       </c>
       <c r="B439" t="s">
-        <v>436</v>
+        <v>458</v>
       </c>
       <c r="C439">
         <v>763</v>
@@ -32908,7 +33066,7 @@
         <v>438</v>
       </c>
       <c r="B440" t="s">
-        <v>437</v>
+        <v>459</v>
       </c>
       <c r="C440">
         <v>833</v>
@@ -32979,7 +33137,7 @@
         <v>439</v>
       </c>
       <c r="B441" t="s">
-        <v>438</v>
+        <v>460</v>
       </c>
       <c r="C441">
         <v>977</v>
@@ -33050,7 +33208,7 @@
         <v>440</v>
       </c>
       <c r="B442" t="s">
-        <v>439</v>
+        <v>461</v>
       </c>
       <c r="C442">
         <v>1093</v>
@@ -33121,7 +33279,7 @@
         <v>441</v>
       </c>
       <c r="B443" t="s">
-        <v>440</v>
+        <v>462</v>
       </c>
       <c r="C443">
         <v>1026</v>
@@ -33192,7 +33350,7 @@
         <v>442</v>
       </c>
       <c r="B444" t="s">
-        <v>441</v>
+        <v>463</v>
       </c>
       <c r="C444">
         <v>925</v>
@@ -33263,7 +33421,7 @@
         <v>443</v>
       </c>
       <c r="B445" t="s">
-        <v>442</v>
+        <v>464</v>
       </c>
       <c r="C445">
         <v>983</v>
@@ -33334,7 +33492,7 @@
         <v>444</v>
       </c>
       <c r="B446" t="s">
-        <v>443</v>
+        <v>465</v>
       </c>
       <c r="C446">
         <v>1019</v>
@@ -33405,7 +33563,7 @@
         <v>445</v>
       </c>
       <c r="B447" t="s">
-        <v>444</v>
+        <v>466</v>
       </c>
       <c r="C447">
         <v>748</v>
@@ -33476,7 +33634,7 @@
         <v>446</v>
       </c>
       <c r="B448" t="s">
-        <v>445</v>
+        <v>467</v>
       </c>
       <c r="C448">
         <v>1178</v>
@@ -33547,7 +33705,7 @@
         <v>447</v>
       </c>
       <c r="B449" t="s">
-        <v>446</v>
+        <v>468</v>
       </c>
       <c r="C449">
         <v>649</v>
@@ -33618,7 +33776,7 @@
         <v>448</v>
       </c>
       <c r="B450" t="s">
-        <v>447</v>
+        <v>469</v>
       </c>
       <c r="C450">
         <v>1088</v>
@@ -33689,7 +33847,7 @@
         <v>449</v>
       </c>
       <c r="B451" t="s">
-        <v>448</v>
+        <v>470</v>
       </c>
       <c r="C451">
         <v>1131</v>
@@ -33760,7 +33918,7 @@
         <v>450</v>
       </c>
       <c r="B452" t="s">
-        <v>449</v>
+        <v>471</v>
       </c>
       <c r="C452">
         <v>1150</v>
@@ -33831,7 +33989,7 @@
         <v>451</v>
       </c>
       <c r="B453" t="s">
-        <v>449</v>
+        <v>471</v>
       </c>
       <c r="C453">
         <v>1039</v>
@@ -33902,7 +34060,7 @@
         <v>452</v>
       </c>
       <c r="B454" t="s">
-        <v>450</v>
+        <v>472</v>
       </c>
       <c r="C454">
         <v>1122</v>
@@ -33973,7 +34131,7 @@
         <v>453</v>
       </c>
       <c r="B455" t="s">
-        <v>451</v>
+        <v>473</v>
       </c>
       <c r="C455">
         <v>938</v>
@@ -34044,7 +34202,7 @@
         <v>454</v>
       </c>
       <c r="B456" t="s">
-        <v>452</v>
+        <v>474</v>
       </c>
       <c r="C456">
         <v>1047</v>
@@ -34115,7 +34273,7 @@
         <v>455</v>
       </c>
       <c r="B457" t="s">
-        <v>453</v>
+        <v>475</v>
       </c>
       <c r="C457">
         <v>1078</v>
@@ -34186,7 +34344,7 @@
         <v>456</v>
       </c>
       <c r="B458" t="s">
-        <v>454</v>
+        <v>476</v>
       </c>
       <c r="C458">
         <v>1043</v>
@@ -34257,7 +34415,7 @@
         <v>457</v>
       </c>
       <c r="B459" t="s">
-        <v>455</v>
+        <v>477</v>
       </c>
       <c r="C459">
         <v>1000</v>
@@ -34328,7 +34486,7 @@
         <v>458</v>
       </c>
       <c r="B460" t="s">
-        <v>456</v>
+        <v>478</v>
       </c>
       <c r="C460">
         <v>915</v>
@@ -34399,7 +34557,7 @@
         <v>459</v>
       </c>
       <c r="B461" t="s">
-        <v>457</v>
+        <v>479</v>
       </c>
       <c r="C461">
         <v>1009</v>
@@ -34470,7 +34628,7 @@
         <v>460</v>
       </c>
       <c r="B462" t="s">
-        <v>458</v>
+        <v>480</v>
       </c>
       <c r="C462">
         <v>1145</v>
@@ -34541,7 +34699,7 @@
         <v>461</v>
       </c>
       <c r="B463" t="s">
-        <v>459</v>
+        <v>481</v>
       </c>
       <c r="C463">
         <v>793</v>
@@ -34612,7 +34770,7 @@
         <v>462</v>
       </c>
       <c r="B464" t="s">
-        <v>460</v>
+        <v>482</v>
       </c>
       <c r="C464">
         <v>888</v>
@@ -34683,7 +34841,7 @@
         <v>463</v>
       </c>
       <c r="B465" t="s">
-        <v>461</v>
+        <v>483</v>
       </c>
       <c r="C465">
         <v>755</v>
@@ -34754,7 +34912,7 @@
         <v>464</v>
       </c>
       <c r="B466" t="s">
-        <v>462</v>
+        <v>484</v>
       </c>
       <c r="C466">
         <v>1021</v>
